--- a/pr-2/StructureDefinition-kpi-definition.xlsx
+++ b/pr-2/StructureDefinition-kpi-definition.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-16T14:28:20+00:00</t>
+    <t>2026-10-26T15:58:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
